--- a/balance_generate/input_data/bank_data.xlsx
+++ b/balance_generate/input_data/bank_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzimi\Documents\data_engineering\data_projects\git_hub_projects\bank_project\balance_generate\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CD3A5B-FD34-449B-820D-67DBDF3A06CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55AD9B5-26E6-4E41-9D01-A9508F3687D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2960" yWindow="2960" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3640" yWindow="3640" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bs_structure" sheetId="2" r:id="rId1"/>
@@ -36,29 +36,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="79">
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>prod_id</t>
-  </si>
-  <si>
     <t>L</t>
   </si>
   <si>
     <t>E</t>
   </si>
   <si>
-    <t>prod_type</t>
-  </si>
-  <si>
     <t>rate_type</t>
   </si>
   <si>
-    <t>mat</t>
-  </si>
-  <si>
     <t>amort_type</t>
   </si>
   <si>
@@ -68,12 +59,6 @@
     <t>fixing_freq</t>
   </si>
   <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>ccy</t>
-  </si>
-  <si>
     <t>PLN</t>
   </si>
   <si>
@@ -83,10 +68,193 @@
     <t>30Y</t>
   </si>
   <si>
-    <t>WIB3M</t>
-  </si>
-  <si>
-    <t>term_depo</t>
+    <t>F</t>
+  </si>
+  <si>
+    <t>7Y</t>
+  </si>
+  <si>
+    <t>5Y</t>
+  </si>
+  <si>
+    <t>6M</t>
+  </si>
+  <si>
+    <t>NM</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>1Y</t>
+  </si>
+  <si>
+    <t>client_type_id</t>
+  </si>
+  <si>
+    <t>bs_percentage</t>
+  </si>
+  <si>
+    <t>report_date</t>
+  </si>
+  <si>
+    <t>bs_side</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>maturity</t>
+  </si>
+  <si>
+    <t>product_code</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>rate_index</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>25Y</t>
+  </si>
+  <si>
+    <t>retained_earnings</t>
+  </si>
+  <si>
+    <t>disc_curve</t>
+  </si>
+  <si>
+    <t>fwd_curve</t>
+  </si>
+  <si>
+    <t>PLN_disc_curve</t>
+  </si>
+  <si>
+    <t>PLN_fwd_curve</t>
+  </si>
+  <si>
+    <t>b_day_conv</t>
+  </si>
+  <si>
+    <t>ModifiedFollowing</t>
+  </si>
+  <si>
+    <t>ACT/365</t>
+  </si>
+  <si>
+    <t>dc_conv</t>
+  </si>
+  <si>
+    <t>PLN_ASK_5Y</t>
+  </si>
+  <si>
+    <t>PLN_ASK_3M</t>
+  </si>
+  <si>
+    <t>PLN_ASK_7Y</t>
+  </si>
+  <si>
+    <t>PLN_ASK_6M</t>
+  </si>
+  <si>
+    <t>PLN_BID_6M</t>
+  </si>
+  <si>
+    <t>PLN_BID_1M</t>
+  </si>
+  <si>
+    <t>LCR</t>
+  </si>
+  <si>
+    <t>issued_bond</t>
+  </si>
+  <si>
+    <t>haircut</t>
+  </si>
+  <si>
+    <t>ASF</t>
+  </si>
+  <si>
+    <t>RSF</t>
+  </si>
+  <si>
+    <t>tier_type</t>
+  </si>
+  <si>
+    <t>hqla_class</t>
+  </si>
+  <si>
+    <t>mortgage_fixed_ind</t>
+  </si>
+  <si>
+    <t>mortgage_float_ind</t>
+  </si>
+  <si>
+    <t>cash_loan_fixed_ind</t>
+  </si>
+  <si>
+    <t>cash_loan_float_ind</t>
+  </si>
+  <si>
+    <t>inv_loan_float_sme</t>
+  </si>
+  <si>
+    <t>bond_fixed_gov</t>
+  </si>
+  <si>
+    <t>bond_float_gov</t>
+  </si>
+  <si>
+    <t>cash_gov</t>
+  </si>
+  <si>
+    <t>term_deposit_ind</t>
+  </si>
+  <si>
+    <t>current_account_ind</t>
+  </si>
+  <si>
+    <t>saving_account_ind</t>
+  </si>
+  <si>
+    <t>term_deposit_bank</t>
+  </si>
+  <si>
+    <t>PLN_ASK_1M</t>
+  </si>
+  <si>
+    <t>current_account_sme</t>
+  </si>
+  <si>
+    <t>own_name</t>
+  </si>
+  <si>
+    <t>mortgage_fixed</t>
+  </si>
+  <si>
+    <t>mortgage_float</t>
+  </si>
+  <si>
+    <t>cash_loan_fixed</t>
+  </si>
+  <si>
+    <t>cash_loan_float</t>
+  </si>
+  <si>
+    <t>bond_fixed</t>
+  </si>
+  <si>
+    <t>bond_float</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>term_deposit</t>
   </si>
   <si>
     <t>current_account</t>
@@ -95,71 +263,32 @@
     <t>saving_account</t>
   </si>
   <si>
-    <t>retained_earinings</t>
-  </si>
-  <si>
-    <t>issued_bond</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>7Y</t>
-  </si>
-  <si>
-    <t>5Y</t>
-  </si>
-  <si>
-    <t>6M</t>
-  </si>
-  <si>
-    <t>NM</t>
-  </si>
-  <si>
-    <t>1M</t>
-  </si>
-  <si>
-    <t>1Y</t>
-  </si>
-  <si>
-    <t>issued_stock</t>
-  </si>
-  <si>
-    <t>client_type_id</t>
-  </si>
-  <si>
-    <t>bs_percentage</t>
-  </si>
-  <si>
-    <t>mortgage_float</t>
-  </si>
-  <si>
-    <t>bond_fixed</t>
-  </si>
-  <si>
-    <t>cash_loan_fixed</t>
-  </si>
-  <si>
-    <t>current_rate</t>
-  </si>
-  <si>
-    <t>report_date</t>
-  </si>
-  <si>
-    <t>bs_side</t>
+    <t>issued_bond_float</t>
+  </si>
+  <si>
+    <t>investment_loan_float</t>
+  </si>
+  <si>
+    <t>common_shares</t>
+  </si>
+  <si>
+    <t>risk_reserves</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -468,251 +597,394 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8188D07C-A870-4194-AE82-5ADE66722983}">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" customWidth="1"/>
     <col min="3" max="3" width="17.08984375" customWidth="1"/>
-    <col min="4" max="4" width="11.26953125" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7265625" customWidth="1"/>
     <col min="7" max="7" width="20.1796875" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="11" max="11" width="12.81640625" customWidth="1"/>
+    <col min="13" max="13" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="12.81640625" customWidth="1"/>
+    <col min="16" max="16" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.7265625" customWidth="1"/>
+    <col min="18" max="18" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.7265625" customWidth="1"/>
+    <col min="21" max="21" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="P1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S1" t="s">
+        <v>48</v>
+      </c>
+      <c r="T1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V1" t="s">
+        <v>45</v>
+      </c>
+      <c r="W1" t="s">
+        <v>46</v>
+      </c>
+      <c r="X1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>45657</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" t="s">
         <v>32</v>
       </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="X2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45657</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>1100</v>
       </c>
       <c r="E3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" t="s">
         <v>34</v>
       </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="Q3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" t="s">
+        <v>32</v>
+      </c>
+      <c r="X3">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>45657</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
+        <v>67</v>
+      </c>
+      <c r="F4" t="s">
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4" t="s">
+        <v>32</v>
+      </c>
+      <c r="X4">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45657</v>
       </c>
       <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>2100</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+      <c r="X5">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45657</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>4100</v>
+      </c>
+      <c r="E6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
         <v>12</v>
       </c>
-      <c r="H6" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" t="s">
         <v>26</v>
       </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+      <c r="X6">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45657</v>
       </c>
@@ -720,124 +992,725 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>3000</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
+        <v>69</v>
+      </c>
+      <c r="F7" t="s">
+        <v>55</v>
       </c>
       <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" t="s">
         <v>12</v>
       </c>
-      <c r="H7" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R7" t="s">
+        <v>32</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>45657</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>3100</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>14</v>
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
       </c>
       <c r="G8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" t="s">
         <v>12</v>
       </c>
-      <c r="I8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N8" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" t="s">
+        <v>35</v>
+      </c>
+      <c r="P8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" t="s">
+        <v>32</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>45657</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3500</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9">
-        <v>8</v>
+        <v>71</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
       </c>
       <c r="G9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" t="s">
         <v>12</v>
       </c>
-      <c r="H9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>45657</v>
       </c>
       <c r="B10">
+        <v>0.5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>7900</v>
+      </c>
+      <c r="E10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10">
         <v>9</v>
       </c>
-      <c r="C10" t="s">
+      <c r="I10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" t="s">
+        <v>62</v>
+      </c>
+      <c r="O10" t="s">
+        <v>35</v>
+      </c>
+      <c r="P10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>7060</v>
+      </c>
+      <c r="E11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" t="s">
+        <v>35</v>
+      </c>
+      <c r="P11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11">
+        <v>0.05</v>
+      </c>
+      <c r="W11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>6000</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+      <c r="I12" t="s">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" t="s">
+        <v>42</v>
+      </c>
+      <c r="O12" t="s">
+        <v>35</v>
+      </c>
+      <c r="P12" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>31</v>
+      </c>
+      <c r="R12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T12">
+        <v>0.05</v>
+      </c>
+      <c r="W12">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>8000</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="I13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13" t="s">
+        <v>15</v>
+      </c>
+      <c r="N13" t="s">
+        <v>42</v>
+      </c>
+      <c r="O13" t="s">
+        <v>35</v>
+      </c>
+      <c r="P13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>31</v>
+      </c>
+      <c r="R13" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13">
+        <v>0.1</v>
+      </c>
+      <c r="W13">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>6300</v>
+      </c>
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+      <c r="L14" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14" t="s">
+        <v>42</v>
+      </c>
+      <c r="O14" t="s">
+        <v>35</v>
+      </c>
+      <c r="P14" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>31</v>
+      </c>
+      <c r="R14" t="s">
+        <v>32</v>
+      </c>
+      <c r="T14">
+        <v>0.05</v>
+      </c>
+      <c r="W14">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>7900</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15">
+        <v>9</v>
+      </c>
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>15</v>
+      </c>
+      <c r="M15" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" t="s">
+        <v>42</v>
+      </c>
+      <c r="O15" t="s">
+        <v>35</v>
+      </c>
+      <c r="P15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>31</v>
+      </c>
+      <c r="R15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>5000</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16">
+        <v>8</v>
+      </c>
+      <c r="I16" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" t="s">
+        <v>12</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M16" t="s">
+        <v>13</v>
+      </c>
+      <c r="N16" t="s">
+        <v>40</v>
+      </c>
+      <c r="O16" t="s">
+        <v>35</v>
+      </c>
+      <c r="P16" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" t="s">
+        <v>32</v>
+      </c>
+      <c r="S16">
+        <v>2</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>5300</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17">
+        <v>14</v>
+      </c>
+      <c r="J17" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" t="s">
+        <v>32</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B18">
         <v>3</v>
       </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" t="s">
-        <v>28</v>
+      <c r="C18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>5100</v>
+      </c>
+      <c r="E18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18">
+        <v>14</v>
+      </c>
+      <c r="J18" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" t="s">
+        <v>32</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>5400</v>
+      </c>
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19">
+        <v>14</v>
+      </c>
+      <c r="J19" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>31</v>
+      </c>
+      <c r="R19" t="s">
+        <v>32</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/balance_generate/input_data/bank_data.xlsx
+++ b/balance_generate/input_data/bank_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzimi\Documents\data_engineering\data_projects\git_hub_projects\bank_project\balance_generate\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55AD9B5-26E6-4E41-9D01-A9508F3687D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9E8C0C-997F-4B5E-B1E8-D77343F261AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3640" yWindow="3640" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bs_structure" sheetId="2" r:id="rId1"/>
@@ -697,7 +697,7 @@
         <v>45657</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
@@ -930,7 +930,7 @@
         <v>45657</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
         <v>0</v>
@@ -1051,7 +1051,7 @@
         <v>45657</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>45657</v>
       </c>
       <c r="B10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>0</v>
@@ -1231,8 +1231,8 @@
       <c r="R10" t="s">
         <v>32</v>
       </c>
-      <c r="W10">
-        <v>1</v>
+      <c r="X10">
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
@@ -1240,7 +1240,7 @@
         <v>45657</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
         <v>1</v>
@@ -1529,7 +1529,7 @@
         <v>45657</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" t="s">
         <v>1</v>
@@ -1673,7 +1673,7 @@
         <v>45657</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
         <v>2</v>

--- a/balance_generate/input_data/bank_data.xlsx
+++ b/balance_generate/input_data/bank_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzimi\Documents\data_engineering\data_projects\git_hub_projects\bank_project\balance_generate\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9E8C0C-997F-4B5E-B1E8-D77343F261AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44D3ECD-6DFA-4DAE-9111-5252BE3646AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="80">
   <si>
     <t>A</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>risk_reserves</t>
+  </si>
+  <si>
+    <t>2M</t>
   </si>
 </sst>
 </file>
@@ -1384,6 +1387,9 @@
       <c r="L13" t="s">
         <v>15</v>
       </c>
+      <c r="M13" t="s">
+        <v>79</v>
+      </c>
       <c r="N13" t="s">
         <v>42</v>
       </c>

--- a/balance_generate/input_data/bank_data.xlsx
+++ b/balance_generate/input_data/bank_data.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -72,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -82,6 +83,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="21.54296875" customWidth="1" min="5" max="5"/>
@@ -1109,7 +1111,7 @@
         <v>45657</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2383,6 +2385,112 @@
         <v>0</v>
       </c>
       <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>t_bill</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>t_bill_gov</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>7D</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>7D</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>PLN_ASK_1M</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>ACT/365</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ModifiedFollowing</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>PLN_disc_curve</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>PLN_fwd_curve</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
         <v>0</v>
       </c>
     </row>

--- a/balance_generate/input_data/bank_data.xlsx
+++ b/balance_generate/input_data/bank_data.xlsx
@@ -1111,7 +1111,7 @@
         <v>45657</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45657</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>45657</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/balance_generate/input_data/bank_data.xlsx
+++ b/balance_generate/input_data/bank_data.xlsx
@@ -801,7 +801,7 @@
         <v>45657</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/balance_generate/input_data/bank_data.xlsx
+++ b/balance_generate/input_data/bank_data.xlsx
@@ -1111,7 +1111,7 @@
         <v>45657</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45657</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45657</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>45657</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0005</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="13">
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0005</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="15">
